--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9478,0.0427,0.0056,0.0011</t>
-  </si>
-  <si>
-    <t>0.7131,0.1324,0.0323,0.0761</t>
-  </si>
-  <si>
-    <t>0.8286,0.1784,0.0115,0.0023</t>
-  </si>
-  <si>
-    <t>0.7829,0.1342,0.0414,0.0146</t>
-  </si>
-  <si>
-    <t>0.9491,0.0315,0.0020,0.0020</t>
-  </si>
-  <si>
-    <t>0.8841,0.1277,0.0045,0.0013</t>
-  </si>
-  <si>
-    <t>0.7998,0.2661,0.0053,0.0015</t>
-  </si>
-  <si>
-    <t>0.7825,0.2067,0.0078,0.0046</t>
-  </si>
-  <si>
-    <t>0.7949,0.2034,0.0095,0.0028</t>
-  </si>
-  <si>
-    <t>0.8869,0.1069,0.0024,0.0019</t>
-  </si>
-  <si>
-    <t>0.7622,0.3153,0.0073,0.0014</t>
-  </si>
-  <si>
-    <t>0.8984,0.0779,0.0019,0.0019</t>
-  </si>
-  <si>
-    <t>0.8809,0.0932,0.0222,0.0007</t>
-  </si>
-  <si>
-    <t>0.8753,0.0568,0.0473,0.0013</t>
-  </si>
-  <si>
-    <t>0.9051,0.0094,0.1427,0.0006</t>
-  </si>
-  <si>
-    <t>0.9130,0.0171,0.1067,0.0013</t>
-  </si>
-  <si>
-    <t>0.9595,0.0252,0.0120,0.0007</t>
-  </si>
-  <si>
-    <t>0.4001,0.7484,0.0084,0.0002</t>
-  </si>
-  <si>
-    <t>0.3600,0.7701,0.0120,0.0007</t>
-  </si>
-  <si>
-    <t>0.6501,0.4827,0.0079,0.0010</t>
-  </si>
-  <si>
-    <t>0.0666,0.9460,0.0146,0.0009</t>
-  </si>
-  <si>
-    <t>0.0964,0.9385,0.0089,0.0004</t>
-  </si>
-  <si>
-    <t>0.8757,0.0578,0.0700,0.0013</t>
-  </si>
-  <si>
-    <t>0.9101,0.0173,0.0966,0.0021</t>
-  </si>
-  <si>
-    <t>0.7435,0.0133,0.3282,0.0006</t>
-  </si>
-  <si>
-    <t>0.8669,0.0461,0.1021,0.0025</t>
-  </si>
-  <si>
-    <t>0.8429,0.0125,0.2382,0.0026</t>
-  </si>
-  <si>
-    <t>0.9158,0.0219,0.0588,0.0017</t>
-  </si>
-  <si>
-    <t>0.8724,0.0049,0.2394,0.0008</t>
-  </si>
-  <si>
-    <t>0.8303,0.1959,0.0192,0.0017</t>
-  </si>
-  <si>
-    <t>0.7643,0.2115,0.0381,0.0021</t>
-  </si>
-  <si>
-    <t>0.0181,0.0328,0.9808,0.0016</t>
-  </si>
-  <si>
-    <t>0.2321,0.6590,0.0532,0.0008</t>
-  </si>
-  <si>
-    <t>0.7167,0.2819,0.0229,0.0037</t>
-  </si>
-  <si>
-    <t>0.8345,0.1935,0.0099,0.0013</t>
-  </si>
-  <si>
-    <t>0.6837,0.4349,0.0099,0.0007</t>
-  </si>
-  <si>
-    <t>0.8676,0.1634,0.0075,0.0003</t>
-  </si>
-  <si>
-    <t>0.1929,0.7326,0.0701,0.0021</t>
-  </si>
-  <si>
-    <t>0.9123,0.0056,0.1404,0.0021</t>
-  </si>
-  <si>
-    <t>0.8929,0.0056,0.1929,0.0005</t>
-  </si>
-  <si>
-    <t>0.9164,0.0081,0.1297,0.0024</t>
-  </si>
-  <si>
-    <t>0.6981,0.0127,0.4735,0.0039</t>
-  </si>
-  <si>
-    <t>0.4909,0.0199,0.5103,0.0013</t>
-  </si>
-  <si>
-    <t>0.8328,0.0115,0.2745,0.0021</t>
-  </si>
-  <si>
-    <t>0.8873,0.0856,0.0192,0.0025</t>
-  </si>
-  <si>
-    <t>0.9205,0.0682,0.0145,0.0004</t>
-  </si>
-  <si>
-    <t>0.7007,0.2881,0.0212,0.0003</t>
-  </si>
-  <si>
-    <t>0.8693,0.0853,0.0321,0.0005</t>
-  </si>
-  <si>
-    <t>0.2822,0.1517,0.7332,0.0045</t>
-  </si>
-  <si>
-    <t>0.4650,0.0159,0.6332,0.0010</t>
-  </si>
-  <si>
-    <t>0.8155,0.0136,0.2806,0.0087</t>
-  </si>
-  <si>
-    <t>0.8024,0.0249,0.2790,0.0030</t>
-  </si>
-  <si>
-    <t>0.1057,0.0242,0.9067,0.0006</t>
-  </si>
-  <si>
-    <t>0.3240,0.0828,0.5560,0.0011</t>
-  </si>
-  <si>
-    <t>0.9136,0.0710,0.0053,0.0019</t>
-  </si>
-  <si>
-    <t>0.9397,0.0431,0.0025,0.0020</t>
-  </si>
-  <si>
-    <t>0.7217,0.3033,0.0092,0.0035</t>
-  </si>
-  <si>
-    <t>0.3460,0.4017,0.5774,0.0173</t>
-  </si>
-  <si>
-    <t>0.8740,0.1245,0.0055,0.0020</t>
-  </si>
-  <si>
-    <t>0.8345,0.1873,0.0079,0.0021</t>
-  </si>
-  <si>
-    <t>0.7057,0.3370,0.0086,0.0031</t>
-  </si>
-  <si>
-    <t>0.0127,0.6310,0.9690,0.0017</t>
-  </si>
-  <si>
-    <t>0.1636,0.0627,0.8960,0.0009</t>
-  </si>
-  <si>
-    <t>0.6719,0.0642,0.3004,0.0026</t>
-  </si>
-  <si>
-    <t>0.0712,0.6969,0.6732,0.0019</t>
-  </si>
-  <si>
-    <t>0.4370,0.0428,0.6917,0.0022</t>
-  </si>
-  <si>
-    <t>0.8771,0.1663,0.0075,0.0001</t>
-  </si>
-  <si>
-    <t>0.0269,0.9746,0.0146,0.0001</t>
-  </si>
-  <si>
-    <t>0.8620,0.1197,0.0334,0.0017</t>
-  </si>
-  <si>
-    <t>0.6678,0.3495,0.0289,0.0013</t>
-  </si>
-  <si>
-    <t>0.1390,0.7063,0.1703,0.0012</t>
-  </si>
-  <si>
-    <t>0.3859,0.1804,0.4036,0.0011</t>
-  </si>
-  <si>
-    <t>0.8408,0.0322,0.1263,0.0007</t>
-  </si>
-  <si>
-    <t>0.0867,0.8570,0.0413,0.0002</t>
-  </si>
-  <si>
-    <t>0.8385,0.0648,0.0450,0.0003</t>
-  </si>
-  <si>
-    <t>0.7437,0.0933,0.1495,0.0460</t>
-  </si>
-  <si>
-    <t>0.9237,0.0198,0.0044,0.0162</t>
-  </si>
-  <si>
-    <t>0.8859,0.0451,0.0195,0.0130</t>
-  </si>
-  <si>
-    <t>0.8996,0.0604,0.0103,0.0068</t>
-  </si>
-  <si>
-    <t>0.9164,0.0204,0.0105,0.0117</t>
-  </si>
-  <si>
-    <t>0.8889,0.0311,0.0295,0.0196</t>
-  </si>
-  <si>
-    <t>0.7001,0.0374,0.3183,0.0006</t>
-  </si>
-  <si>
-    <t>0.3491,0.1889,0.5272,0.0041</t>
-  </si>
-  <si>
-    <t>0.4487,0.0330,0.5389,0.0003</t>
-  </si>
-  <si>
-    <t>0.7004,0.1029,0.1661,0.0009</t>
-  </si>
-  <si>
-    <t>0.5391,0.1191,0.2413,0.0009</t>
-  </si>
-  <si>
-    <t>0.7991,0.0825,0.0534,0.0002</t>
-  </si>
-  <si>
-    <t>0.8361,0.1980,0.0063,0.0019</t>
-  </si>
-  <si>
-    <t>0.8905,0.1408,0.0022,0.0011</t>
-  </si>
-  <si>
-    <t>0.9032,0.0699,0.0030,0.0029</t>
-  </si>
-  <si>
-    <t>0.6789,0.3310,0.0135,0.0047</t>
-  </si>
-  <si>
-    <t>0.6354,0.4320,0.0097,0.0030</t>
-  </si>
-  <si>
-    <t>0.7796,0.2562,0.0035,0.0019</t>
-  </si>
-  <si>
-    <t>0.9062,0.0897,0.0030,0.0016</t>
-  </si>
-  <si>
-    <t>0.7123,0.3350,0.0165,0.0033</t>
-  </si>
-  <si>
-    <t>0.8705,0.1609,0.0033,0.0014</t>
-  </si>
-  <si>
-    <t>0.9543,0.0295,0.0027,0.0018</t>
-  </si>
-  <si>
-    <t>0.6468,0.2815,0.0049,0.0042</t>
-  </si>
-  <si>
-    <t>0.9453,0.0540,0.0019,0.0012</t>
-  </si>
-  <si>
-    <t>0.8573,0.1387,0.0019,0.0017</t>
-  </si>
-  <si>
-    <t>0.8225,0.1987,0.0042,0.0014</t>
-  </si>
-  <si>
-    <t>0.8766,0.1035,0.0019,0.0020</t>
-  </si>
-  <si>
-    <t>0.7733,0.2679,0.0084,0.0027</t>
-  </si>
-  <si>
-    <t>0.1399,0.1972,0.8116,0.0069</t>
-  </si>
-  <si>
-    <t>0.4389,0.1190,0.4073,0.0010</t>
-  </si>
-  <si>
-    <t>0.7635,0.1109,0.1182,0.0040</t>
-  </si>
-  <si>
-    <t>0.9480,0.0069,0.0645,0.0017</t>
-  </si>
-  <si>
-    <t>0.4919,0.6148,0.0141,0.0017</t>
-  </si>
-  <si>
-    <t>0.7808,0.2759,0.0048,0.0009</t>
-  </si>
-  <si>
-    <t>0.3430,0.7849,0.0151,0.0009</t>
-  </si>
-  <si>
-    <t>0.6087,0.4949,0.0239,0.0011</t>
-  </si>
-  <si>
-    <t>0.6538,0.5130,0.0056,0.0008</t>
-  </si>
-  <si>
-    <t>0.5665,0.5861,0.0116,0.0008</t>
-  </si>
-  <si>
-    <t>0.7396,0.3866,0.0091,0.0010</t>
-  </si>
-  <si>
-    <t>0.8460,0.0820,0.0434,0.0035</t>
-  </si>
-  <si>
-    <t>0.7209,0.0165,0.4064,0.0047</t>
-  </si>
-  <si>
-    <t>0.9672,0.0118,0.0148,0.0007</t>
-  </si>
-  <si>
-    <t>0.8849,0.0578,0.0581,0.0034</t>
-  </si>
-  <si>
-    <t>0.8588,0.0561,0.0932,0.0055</t>
-  </si>
-  <si>
-    <t>0.7064,0.2663,0.0242,0.0002</t>
-  </si>
-  <si>
-    <t>0.9082,0.0809,0.0101,0.0003</t>
-  </si>
-  <si>
-    <t>0.5875,0.4919,0.0151,0.0007</t>
-  </si>
-  <si>
-    <t>0.1168,0.3655,0.4435,0.0007</t>
-  </si>
-  <si>
-    <t>0.8892,0.1398,0.0060,0.0003</t>
-  </si>
-  <si>
-    <t>0.7457,0.3356,0.0083,0.0014</t>
-  </si>
-  <si>
-    <t>0.9077,0.1161,0.0033,0.0005</t>
-  </si>
-  <si>
-    <t>0.9014,0.1251,0.0071,0.0006</t>
-  </si>
-  <si>
-    <t>0.8282,0.1559,0.0151,0.0055</t>
-  </si>
-  <si>
-    <t>0.9487,0.0543,0.0019,0.0005</t>
-  </si>
-  <si>
-    <t>0.8236,0.1998,0.0094,0.0024</t>
-  </si>
-  <si>
-    <t>0.8663,0.1723,0.0074,0.0013</t>
-  </si>
-  <si>
-    <t>0.7608,0.3519,0.0138,0.0011</t>
-  </si>
-  <si>
-    <t>0.8032,0.2487,0.0090,0.0013</t>
-  </si>
-  <si>
-    <t>0.8757,0.1148,0.0128,0.0050</t>
-  </si>
-  <si>
-    <t>0.9569,0.0050,0.0612,0.0003</t>
-  </si>
-  <si>
-    <t>0.4085,0.0381,0.7468,0.0013</t>
-  </si>
-  <si>
-    <t>0.7831,0.0051,0.3910,0.0017</t>
-  </si>
-  <si>
-    <t>0.7097,0.0148,0.4042,0.0013</t>
-  </si>
-  <si>
-    <t>0.9680,0.0080,0.0164,0.0009</t>
-  </si>
-  <si>
-    <t>0.9207,0.0414,0.0248,0.0017</t>
-  </si>
-  <si>
-    <t>0.8093,0.0527,0.1549,0.0017</t>
-  </si>
-  <si>
-    <t>0.8250,0.1036,0.0706,0.0019</t>
-  </si>
-  <si>
-    <t>0.9427,0.0258,0.0057,0.0038</t>
-  </si>
-  <si>
-    <t>0.7119,0.0182,0.0604,0.1905</t>
-  </si>
-  <si>
-    <t>0.9270,0.0237,0.0114,0.0092</t>
-  </si>
-  <si>
-    <t>0.9583,0.0161,0.0070,0.0029</t>
-  </si>
-  <si>
-    <t>0.3595,0.5982,0.0534,0.0007</t>
-  </si>
-  <si>
-    <t>0.9367,0.0579,0.0016,0.0012</t>
-  </si>
-  <si>
-    <t>0.7275,0.3428,0.0140,0.0012</t>
-  </si>
-  <si>
-    <t>0.9467,0.0177,0.0015,0.0049</t>
-  </si>
-  <si>
-    <t>0.8853,0.1236,0.0194,0.0017</t>
-  </si>
-  <si>
-    <t>0.8408,0.1540,0.0087,0.0010</t>
-  </si>
-  <si>
-    <t>0.6010,0.3918,0.0764,0.0129</t>
-  </si>
-  <si>
-    <t>0.6938,0.2964,0.0454,0.0101</t>
-  </si>
-  <si>
-    <t>0.2813,0.0738,0.7431,0.0437</t>
-  </si>
-  <si>
-    <t>0.7189,0.2444,0.0488,0.0051</t>
-  </si>
-  <si>
-    <t>0.8788,0.0804,0.0069,0.0059</t>
-  </si>
-  <si>
-    <t>0.4928,0.6322,0.0110,0.0007</t>
-  </si>
-  <si>
-    <t>0.7437,0.3347,0.0107,0.0007</t>
-  </si>
-  <si>
-    <t>0.7799,0.2194,0.0133,0.0034</t>
-  </si>
-  <si>
-    <t>0.7824,0.1471,0.0666,0.0021</t>
-  </si>
-  <si>
-    <t>0.7573,0.2499,0.0383,0.0014</t>
-  </si>
-  <si>
-    <t>0.9229,0.0679,0.0135,0.0008</t>
-  </si>
-  <si>
-    <t>0.7201,0.2817,0.0074,0.0028</t>
-  </si>
-  <si>
-    <t>0.9061,0.0987,0.0022,0.0014</t>
-  </si>
-  <si>
-    <t>0.7080,0.3674,0.0163,0.0026</t>
-  </si>
-  <si>
-    <t>0.8889,0.0717,0.0023,0.0034</t>
-  </si>
-  <si>
-    <t>0.7088,0.2957,0.0146,0.0041</t>
-  </si>
-  <si>
-    <t>0.8261,0.1386,0.0098,0.0063</t>
-  </si>
-  <si>
-    <t>0.7739,0.1911,0.0029,0.0027</t>
-  </si>
-  <si>
-    <t>0.6306,0.3939,0.0262,0.0055</t>
-  </si>
-  <si>
-    <t>0.5593,0.5594,0.0062,0.0009</t>
-  </si>
-  <si>
-    <t>0.7474,0.3316,0.0105,0.0007</t>
-  </si>
-  <si>
-    <t>0.7285,0.3380,0.0083,0.0011</t>
-  </si>
-  <si>
-    <t>0.1819,0.8130,0.0741,0.0013</t>
-  </si>
-  <si>
-    <t>0.8595,0.1598,0.0029,0.0012</t>
-  </si>
-  <si>
-    <t>0.7322,0.3016,0.0139,0.0036</t>
-  </si>
-  <si>
-    <t>0.8856,0.1190,0.0058,0.0023</t>
-  </si>
-  <si>
-    <t>0.9140,0.0654,0.0024,0.0016</t>
-  </si>
-  <si>
-    <t>0.0072,0.7923,0.9561,0.0013</t>
-  </si>
-  <si>
-    <t>0.9111,0.0779,0.0043,0.0016</t>
-  </si>
-  <si>
-    <t>0.7899,0.0045,0.3755,0.0005</t>
-  </si>
-  <si>
-    <t>0.8491,0.0406,0.1528,0.0015</t>
-  </si>
-  <si>
-    <t>0.4716,0.3510,0.1481,0.0019</t>
-  </si>
-  <si>
-    <t>0.6108,0.1280,0.1659,0.0002</t>
-  </si>
-  <si>
-    <t>0.7808,0.0213,0.3083,0.0020</t>
-  </si>
-  <si>
-    <t>0.7711,0.0064,0.3619,0.0015</t>
-  </si>
-  <si>
-    <t>0.1050,0.0434,0.9172,0.0021</t>
-  </si>
-  <si>
-    <t>0.6002,0.2603,0.1409,0.0063</t>
-  </si>
-  <si>
-    <t>0.9555,0.0136,0.0243,0.0012</t>
-  </si>
-  <si>
-    <t>0.9642,0.0142,0.0153,0.0008</t>
-  </si>
-  <si>
-    <t>0.8136,0.2148,0.0183,0.0009</t>
-  </si>
-  <si>
-    <t>0.6324,0.1864,0.1346,0.0019</t>
-  </si>
-  <si>
-    <t>0.7631,0.1705,0.0538,0.0009</t>
-  </si>
-  <si>
-    <t>0.7855,0.1365,0.0896,0.0026</t>
-  </si>
-  <si>
-    <t>0.7633,0.1252,0.1067,0.0047</t>
-  </si>
-  <si>
-    <t>0.5625,0.6025,0.0085,0.0009</t>
-  </si>
-  <si>
-    <t>0.5997,0.5588,0.0083,0.0015</t>
-  </si>
-  <si>
-    <t>0.1560,0.9044,0.0069,0.0008</t>
-  </si>
-  <si>
-    <t>0.9323,0.0903,0.0016,0.0009</t>
-  </si>
-  <si>
-    <t>0.9223,0.0554,0.0036,0.0024</t>
-  </si>
-  <si>
-    <t>0.9215,0.0542,0.0183,0.0013</t>
-  </si>
-  <si>
-    <t>0.9113,0.0584,0.0182,0.0012</t>
-  </si>
-  <si>
-    <t>0.9603,0.0129,0.0193,0.0007</t>
-  </si>
-  <si>
-    <t>0.6517,0.1546,0.2500,0.0069</t>
-  </si>
-  <si>
-    <t>0.9288,0.0250,0.0471,0.0025</t>
-  </si>
-  <si>
-    <t>0.0383,0.2024,0.8385,0.0014</t>
-  </si>
-  <si>
-    <t>0.9428,0.0118,0.0437,0.0011</t>
-  </si>
-  <si>
-    <t>0.9338,0.0078,0.0862,0.0008</t>
-  </si>
-  <si>
-    <t>0.9741,0.0021,0.0392,0.0003</t>
-  </si>
-  <si>
-    <t>0.9139,0.0231,0.0379,0.0005</t>
-  </si>
-  <si>
-    <t>0.8292,0.1562,0.0084,0.0047</t>
-  </si>
-  <si>
-    <t>0.6191,0.4202,0.0152,0.0038</t>
-  </si>
-  <si>
-    <t>0.9386,0.0474,0.0021,0.0023</t>
-  </si>
-  <si>
-    <t>0.7977,0.2424,0.0065,0.0013</t>
-  </si>
-  <si>
-    <t>0.8184,0.2244,0.0069,0.0013</t>
-  </si>
-  <si>
-    <t>0.8076,0.1574,0.0053,0.0028</t>
-  </si>
-  <si>
-    <t>0.7681,0.2180,0.0096,0.0060</t>
-  </si>
-  <si>
-    <t>0.9338,0.0620,0.0028,0.0015</t>
-  </si>
-  <si>
-    <t>0.7065,0.1653,0.1343,0.0042</t>
-  </si>
-  <si>
-    <t>0.6664,0.3285,0.0399,0.0038</t>
-  </si>
-  <si>
-    <t>0.6732,0.2931,0.0697,0.0072</t>
-  </si>
-  <si>
-    <t>0.4951,0.0122,0.6918,0.0014</t>
-  </si>
-  <si>
-    <t>0.2109,0.2235,0.6376,0.0020</t>
-  </si>
-  <si>
-    <t>0.7998,0.0082,0.3628,0.0015</t>
-  </si>
-  <si>
-    <t>0.1008,0.0057,0.9518,0.0008</t>
-  </si>
-  <si>
-    <t>0.6484,0.0172,0.4338,0.0011</t>
-  </si>
-  <si>
-    <t>0.0135,0.0401,0.9596,0.0148</t>
-  </si>
-  <si>
-    <t>0.9361,0.0027,0.1440,0.0007</t>
-  </si>
-  <si>
-    <t>0.6057,0.1902,0.1783,0.0025</t>
-  </si>
-  <si>
-    <t>0.9225,0.0272,0.0254,0.0031</t>
-  </si>
-  <si>
-    <t>0.9303,0.0220,0.0504,0.0016</t>
-  </si>
-  <si>
-    <t>0.8954,0.0461,0.0426,0.0030</t>
-  </si>
-  <si>
-    <t>0.9086,0.1201,0.0040,0.0009</t>
-  </si>
-  <si>
-    <t>0.8627,0.0785,0.0017,0.0033</t>
-  </si>
-  <si>
-    <t>0.8876,0.1158,0.0052,0.0030</t>
-  </si>
-  <si>
-    <t>0.8225,0.2386,0.0053,0.0016</t>
-  </si>
-  <si>
-    <t>0.9263,0.0443,0.0012,0.0019</t>
-  </si>
-  <si>
-    <t>0.8585,0.1364,0.0061,0.0033</t>
-  </si>
-  <si>
-    <t>0.9379,0.0594,0.0028,0.0009</t>
-  </si>
-  <si>
-    <t>0.8209,0.2341,0.0043,0.0016</t>
-  </si>
-  <si>
-    <t>0.8649,0.0231,0.1324,0.0013</t>
-  </si>
-  <si>
-    <t>0.6428,0.0277,0.4104,0.0011</t>
-  </si>
-  <si>
-    <t>0.6761,0.0457,0.3357,0.0027</t>
-  </si>
-  <si>
-    <t>0.9528,0.0076,0.0476,0.0005</t>
-  </si>
-  <si>
-    <t>0.6966,0.0139,0.4675,0.0042</t>
-  </si>
-  <si>
-    <t>0.9401,0.0043,0.0762,0.0012</t>
-  </si>
-  <si>
-    <t>0.9101,0.0094,0.1396,0.0014</t>
-  </si>
-  <si>
-    <t>0.9625,0.0030,0.0503,0.0006</t>
-  </si>
-  <si>
-    <t>0.9312,0.0418,0.0145,0.0020</t>
-  </si>
-  <si>
-    <t>0.9706,0.0084,0.0101,0.0013</t>
-  </si>
-  <si>
-    <t>0.8276,0.1708,0.0079,0.0044</t>
-  </si>
-  <si>
-    <t>0.8662,0.0509,0.0696,0.0112</t>
-  </si>
-  <si>
-    <t>0.8464,0.1417,0.0237,0.0039</t>
-  </si>
-  <si>
-    <t>0.7949,0.1592,0.0478,0.0039</t>
+    <t>0.7404,0.3161,0.0150,0.0016</t>
+  </si>
+  <si>
+    <t>0.8781,0.0196,0.0205,0.0282</t>
+  </si>
+  <si>
+    <t>0.8214,0.1483,0.0177,0.0038</t>
+  </si>
+  <si>
+    <t>0.8661,0.0635,0.0232,0.0119</t>
+  </si>
+  <si>
+    <t>0.9020,0.1166,0.0031,0.0014</t>
+  </si>
+  <si>
+    <t>0.7467,0.3599,0.0048,0.0010</t>
+  </si>
+  <si>
+    <t>0.8446,0.1900,0.0071,0.0014</t>
+  </si>
+  <si>
+    <t>0.4174,0.6234,0.0392,0.0051</t>
+  </si>
+  <si>
+    <t>0.8803,0.1273,0.0024,0.0012</t>
+  </si>
+  <si>
+    <t>0.7104,0.3525,0.0112,0.0018</t>
+  </si>
+  <si>
+    <t>0.4631,0.6007,0.0284,0.0045</t>
+  </si>
+  <si>
+    <t>0.9099,0.1136,0.0031,0.0008</t>
+  </si>
+  <si>
+    <t>0.8951,0.0652,0.0211,0.0003</t>
+  </si>
+  <si>
+    <t>0.9265,0.0179,0.0560,0.0029</t>
+  </si>
+  <si>
+    <t>0.7913,0.0843,0.1021,0.0017</t>
+  </si>
+  <si>
+    <t>0.9342,0.0050,0.0997,0.0015</t>
+  </si>
+  <si>
+    <t>0.8600,0.1124,0.0288,0.0016</t>
+  </si>
+  <si>
+    <t>0.6916,0.4495,0.0068,0.0002</t>
+  </si>
+  <si>
+    <t>0.3739,0.7111,0.0283,0.0016</t>
+  </si>
+  <si>
+    <t>0.8320,0.2306,0.0053,0.0005</t>
+  </si>
+  <si>
+    <t>0.0688,0.9587,0.0048,0.0002</t>
+  </si>
+  <si>
+    <t>0.2097,0.8861,0.0069,0.0004</t>
+  </si>
+  <si>
+    <t>0.8446,0.0492,0.1240,0.0017</t>
+  </si>
+  <si>
+    <t>0.9723,0.0031,0.0358,0.0004</t>
+  </si>
+  <si>
+    <t>0.9597,0.0058,0.0425,0.0011</t>
+  </si>
+  <si>
+    <t>0.9218,0.0141,0.0844,0.0006</t>
+  </si>
+  <si>
+    <t>0.9515,0.0163,0.0289,0.0010</t>
+  </si>
+  <si>
+    <t>0.8503,0.0082,0.2706,0.0020</t>
+  </si>
+  <si>
+    <t>0.7929,0.0183,0.3092,0.0019</t>
+  </si>
+  <si>
+    <t>0.7045,0.3937,0.0155,0.0011</t>
+  </si>
+  <si>
+    <t>0.8946,0.0564,0.0470,0.0011</t>
+  </si>
+  <si>
+    <t>0.0634,0.4234,0.8977,0.0052</t>
+  </si>
+  <si>
+    <t>0.0857,0.7967,0.0695,0.0002</t>
+  </si>
+  <si>
+    <t>0.8580,0.1434,0.0038,0.0017</t>
+  </si>
+  <si>
+    <t>0.9535,0.0359,0.0074,0.0011</t>
+  </si>
+  <si>
+    <t>0.7315,0.3037,0.0155,0.0026</t>
+  </si>
+  <si>
+    <t>0.8119,0.1832,0.0348,0.0011</t>
+  </si>
+  <si>
+    <t>0.7845,0.0779,0.1035,0.0018</t>
+  </si>
+  <si>
+    <t>0.9624,0.0007,0.0755,0.0009</t>
+  </si>
+  <si>
+    <t>0.9330,0.0069,0.1085,0.0004</t>
+  </si>
+  <si>
+    <t>0.8669,0.0035,0.2692,0.0009</t>
+  </si>
+  <si>
+    <t>0.8867,0.0144,0.1517,0.0006</t>
+  </si>
+  <si>
+    <t>0.3440,0.2764,0.1717,0.0007</t>
+  </si>
+  <si>
+    <t>0.8293,0.0166,0.2496,0.0021</t>
+  </si>
+  <si>
+    <t>0.5527,0.5372,0.0229,0.0008</t>
+  </si>
+  <si>
+    <t>0.8863,0.1231,0.0077,0.0002</t>
+  </si>
+  <si>
+    <t>0.8758,0.0844,0.0246,0.0005</t>
+  </si>
+  <si>
+    <t>0.8862,0.1098,0.0126,0.0002</t>
+  </si>
+  <si>
+    <t>0.1396,0.1648,0.8129,0.0077</t>
+  </si>
+  <si>
+    <t>0.2820,0.0541,0.7561,0.0016</t>
+  </si>
+  <si>
+    <t>0.6712,0.0226,0.3645,0.0007</t>
+  </si>
+  <si>
+    <t>0.2386,0.0650,0.7294,0.0031</t>
+  </si>
+  <si>
+    <t>0.6230,0.0040,0.5554,0.0004</t>
+  </si>
+  <si>
+    <t>0.7272,0.0188,0.3602,0.0014</t>
+  </si>
+  <si>
+    <t>0.8259,0.1701,0.0079,0.0026</t>
+  </si>
+  <si>
+    <t>0.9680,0.0268,0.0017,0.0007</t>
+  </si>
+  <si>
+    <t>0.8457,0.1982,0.0028,0.0016</t>
+  </si>
+  <si>
+    <t>0.2543,0.5543,0.4742,0.0195</t>
+  </si>
+  <si>
+    <t>0.9806,0.0086,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.7362,0.2989,0.0141,0.0023</t>
+  </si>
+  <si>
+    <t>0.8856,0.1038,0.0042,0.0021</t>
+  </si>
+  <si>
+    <t>0.2246,0.3884,0.6133,0.0030</t>
+  </si>
+  <si>
+    <t>0.9037,0.0022,0.2448,0.0009</t>
+  </si>
+  <si>
+    <t>0.6138,0.0830,0.4734,0.0048</t>
+  </si>
+  <si>
+    <t>0.3259,0.0467,0.6752,0.0004</t>
+  </si>
+  <si>
+    <t>0.3839,0.0449,0.7185,0.0014</t>
+  </si>
+  <si>
+    <t>0.8739,0.1618,0.0063,0.0001</t>
+  </si>
+  <si>
+    <t>0.1713,0.8669,0.0158,0.0007</t>
+  </si>
+  <si>
+    <t>0.7258,0.1628,0.1015,0.0024</t>
+  </si>
+  <si>
+    <t>0.8368,0.2051,0.0090,0.0004</t>
+  </si>
+  <si>
+    <t>0.0450,0.3012,0.9127,0.0047</t>
+  </si>
+  <si>
+    <t>0.7476,0.0062,0.4585,0.0007</t>
+  </si>
+  <si>
+    <t>0.8153,0.0417,0.1798,0.0012</t>
+  </si>
+  <si>
+    <t>0.8473,0.0355,0.0969,0.0007</t>
+  </si>
+  <si>
+    <t>0.2355,0.4392,0.1524,0.0006</t>
+  </si>
+  <si>
+    <t>0.6294,0.1942,0.2812,0.0382</t>
+  </si>
+  <si>
+    <t>0.9098,0.0230,0.0039,0.0134</t>
+  </si>
+  <si>
+    <t>0.9181,0.0148,0.0137,0.0209</t>
+  </si>
+  <si>
+    <t>0.8610,0.0402,0.0113,0.0290</t>
+  </si>
+  <si>
+    <t>0.9523,0.0087,0.0074,0.0130</t>
+  </si>
+  <si>
+    <t>0.8091,0.1072,0.0193,0.0155</t>
+  </si>
+  <si>
+    <t>0.5427,0.0598,0.3911,0.0014</t>
+  </si>
+  <si>
+    <t>0.6659,0.0254,0.4209,0.0025</t>
+  </si>
+  <si>
+    <t>0.3575,0.0562,0.6556,0.0011</t>
+  </si>
+  <si>
+    <t>0.5722,0.1895,0.0781,0.0002</t>
+  </si>
+  <si>
+    <t>0.0516,0.7152,0.5258,0.0005</t>
+  </si>
+  <si>
+    <t>0.9585,0.0035,0.0587,0.0002</t>
+  </si>
+  <si>
+    <t>0.9027,0.1027,0.0031,0.0012</t>
+  </si>
+  <si>
+    <t>0.8562,0.1478,0.0067,0.0016</t>
+  </si>
+  <si>
+    <t>0.8004,0.2066,0.0053,0.0026</t>
+  </si>
+  <si>
+    <t>0.5603,0.5491,0.0166,0.0018</t>
+  </si>
+  <si>
+    <t>0.8833,0.1016,0.0024,0.0020</t>
+  </si>
+  <si>
+    <t>0.7009,0.3334,0.0082,0.0035</t>
+  </si>
+  <si>
+    <t>0.8623,0.1575,0.0049,0.0014</t>
+  </si>
+  <si>
+    <t>0.6414,0.4065,0.0106,0.0034</t>
+  </si>
+  <si>
+    <t>0.9546,0.0368,0.0031,0.0013</t>
+  </si>
+  <si>
+    <t>0.8177,0.2060,0.0069,0.0031</t>
+  </si>
+  <si>
+    <t>0.6964,0.3247,0.0178,0.0041</t>
+  </si>
+  <si>
+    <t>0.8188,0.2183,0.0042,0.0012</t>
+  </si>
+  <si>
+    <t>0.7428,0.3145,0.0075,0.0021</t>
+  </si>
+  <si>
+    <t>0.6802,0.3813,0.0109,0.0017</t>
+  </si>
+  <si>
+    <t>0.8979,0.1405,0.0026,0.0008</t>
+  </si>
+  <si>
+    <t>0.6970,0.3215,0.0159,0.0035</t>
+  </si>
+  <si>
+    <t>0.0847,0.2852,0.8782,0.0138</t>
+  </si>
+  <si>
+    <t>0.9418,0.0094,0.0472,0.0004</t>
+  </si>
+  <si>
+    <t>0.9569,0.0124,0.0204,0.0006</t>
+  </si>
+  <si>
+    <t>0.9096,0.0185,0.0945,0.0017</t>
+  </si>
+  <si>
+    <t>0.1887,0.8588,0.0204,0.0009</t>
+  </si>
+  <si>
+    <t>0.2825,0.8010,0.0118,0.0015</t>
+  </si>
+  <si>
+    <t>0.2730,0.8411,0.0064,0.0008</t>
+  </si>
+  <si>
+    <t>0.5462,0.6295,0.0079,0.0006</t>
+  </si>
+  <si>
+    <t>0.1316,0.8976,0.0165,0.0013</t>
+  </si>
+  <si>
+    <t>0.1114,0.9123,0.0160,0.0004</t>
+  </si>
+  <si>
+    <t>0.9646,0.0315,0.0022,0.0004</t>
+  </si>
+  <si>
+    <t>0.8548,0.1265,0.0272,0.0024</t>
+  </si>
+  <si>
+    <t>0.9103,0.0116,0.1132,0.0026</t>
+  </si>
+  <si>
+    <t>0.9469,0.0132,0.0387,0.0024</t>
+  </si>
+  <si>
+    <t>0.9278,0.0390,0.0220,0.0011</t>
+  </si>
+  <si>
+    <t>0.7271,0.1876,0.1232,0.0139</t>
+  </si>
+  <si>
+    <t>0.8775,0.1662,0.0061,0.0001</t>
+  </si>
+  <si>
+    <t>0.3285,0.6912,0.0113,0.0001</t>
+  </si>
+  <si>
+    <t>0.6857,0.3000,0.0652,0.0019</t>
+  </si>
+  <si>
+    <t>0.3673,0.6242,0.0169,0.0003</t>
+  </si>
+  <si>
+    <t>0.8799,0.1586,0.0046,0.0004</t>
+  </si>
+  <si>
+    <t>0.7263,0.3194,0.0188,0.0018</t>
+  </si>
+  <si>
+    <t>0.4605,0.5842,0.0137,0.0026</t>
+  </si>
+  <si>
+    <t>0.8576,0.1985,0.0060,0.0006</t>
+  </si>
+  <si>
+    <t>0.9402,0.0541,0.0024,0.0018</t>
+  </si>
+  <si>
+    <t>0.7920,0.2729,0.0108,0.0020</t>
+  </si>
+  <si>
+    <t>0.8177,0.2066,0.0164,0.0022</t>
+  </si>
+  <si>
+    <t>0.8227,0.2147,0.0112,0.0020</t>
+  </si>
+  <si>
+    <t>0.9288,0.0790,0.0042,0.0011</t>
+  </si>
+  <si>
+    <t>0.6584,0.4403,0.0040,0.0011</t>
+  </si>
+  <si>
+    <t>0.8035,0.2422,0.0056,0.0018</t>
+  </si>
+  <si>
+    <t>0.6969,0.0111,0.5323,0.0026</t>
+  </si>
+  <si>
+    <t>0.7047,0.0066,0.5138,0.0010</t>
+  </si>
+  <si>
+    <t>0.8159,0.0048,0.3299,0.0012</t>
+  </si>
+  <si>
+    <t>0.6690,0.0059,0.5566,0.0021</t>
+  </si>
+  <si>
+    <t>0.9036,0.0678,0.0151,0.0015</t>
+  </si>
+  <si>
+    <t>0.9607,0.0178,0.0120,0.0008</t>
+  </si>
+  <si>
+    <t>0.8251,0.0539,0.1619,0.0043</t>
+  </si>
+  <si>
+    <t>0.9489,0.0278,0.0116,0.0005</t>
+  </si>
+  <si>
+    <t>0.9214,0.0320,0.0166,0.0066</t>
+  </si>
+  <si>
+    <t>0.8194,0.0652,0.0825,0.0419</t>
+  </si>
+  <si>
+    <t>0.9436,0.0099,0.0075,0.0155</t>
+  </si>
+  <si>
+    <t>0.9316,0.0202,0.0107,0.0108</t>
+  </si>
+  <si>
+    <t>0.3524,0.5590,0.0305,0.0002</t>
+  </si>
+  <si>
+    <t>0.5998,0.4462,0.0187,0.0084</t>
+  </si>
+  <si>
+    <t>0.7643,0.2291,0.0237,0.0037</t>
+  </si>
+  <si>
+    <t>0.8050,0.1526,0.0142,0.0061</t>
+  </si>
+  <si>
+    <t>0.5482,0.5746,0.0150,0.0016</t>
+  </si>
+  <si>
+    <t>0.8992,0.1053,0.0067,0.0015</t>
+  </si>
+  <si>
+    <t>0.9099,0.0560,0.0159,0.0039</t>
+  </si>
+  <si>
+    <t>0.8199,0.2068,0.0054,0.0017</t>
+  </si>
+  <si>
+    <t>0.3268,0.3532,0.6216,0.0176</t>
+  </si>
+  <si>
+    <t>0.9004,0.0497,0.0289,0.0050</t>
+  </si>
+  <si>
+    <t>0.7527,0.2098,0.0239,0.0089</t>
+  </si>
+  <si>
+    <t>0.5623,0.5342,0.0227,0.0011</t>
+  </si>
+  <si>
+    <t>0.7499,0.1948,0.0092,0.0040</t>
+  </si>
+  <si>
+    <t>0.8197,0.2315,0.0105,0.0017</t>
+  </si>
+  <si>
+    <t>0.8738,0.0791,0.0344,0.0036</t>
+  </si>
+  <si>
+    <t>0.8532,0.1470,0.0160,0.0013</t>
+  </si>
+  <si>
+    <t>0.8558,0.1829,0.0095,0.0017</t>
+  </si>
+  <si>
+    <t>0.7018,0.3629,0.0139,0.0031</t>
+  </si>
+  <si>
+    <t>0.9211,0.0319,0.0006,0.0028</t>
+  </si>
+  <si>
+    <t>0.7944,0.2108,0.0046,0.0034</t>
+  </si>
+  <si>
+    <t>0.8752,0.1285,0.0035,0.0017</t>
+  </si>
+  <si>
+    <t>0.9359,0.0445,0.0019,0.0020</t>
+  </si>
+  <si>
+    <t>0.8226,0.1543,0.0146,0.0059</t>
+  </si>
+  <si>
+    <t>0.7659,0.3116,0.0096,0.0011</t>
+  </si>
+  <si>
+    <t>0.8985,0.1034,0.0053,0.0030</t>
+  </si>
+  <si>
+    <t>0.8188,0.1976,0.0225,0.0013</t>
+  </si>
+  <si>
+    <t>0.7577,0.2493,0.0144,0.0039</t>
+  </si>
+  <si>
+    <t>0.6114,0.4791,0.0216,0.0019</t>
+  </si>
+  <si>
+    <t>0.3582,0.5704,0.2128,0.0043</t>
+  </si>
+  <si>
+    <t>0.8186,0.1846,0.0024,0.0018</t>
+  </si>
+  <si>
+    <t>0.9275,0.0557,0.0069,0.0021</t>
+  </si>
+  <si>
+    <t>0.7720,0.2994,0.0098,0.0022</t>
+  </si>
+  <si>
+    <t>0.5902,0.4631,0.0371,0.0029</t>
+  </si>
+  <si>
+    <t>0.0561,0.0542,0.9247,0.0019</t>
+  </si>
+  <si>
+    <t>0.9435,0.0506,0.0038,0.0007</t>
+  </si>
+  <si>
+    <t>0.1724,0.0043,0.8979,0.0006</t>
+  </si>
+  <si>
+    <t>0.8212,0.0044,0.3668,0.0007</t>
+  </si>
+  <si>
+    <t>0.8932,0.0076,0.1975,0.0023</t>
+  </si>
+  <si>
+    <t>0.3687,0.1144,0.6960,0.0014</t>
+  </si>
+  <si>
+    <t>0.2186,0.2728,0.4875,0.0009</t>
+  </si>
+  <si>
+    <t>0.8535,0.0078,0.2638,0.0013</t>
+  </si>
+  <si>
+    <t>0.7995,0.0553,0.2202,0.0024</t>
+  </si>
+  <si>
+    <t>0.9357,0.0136,0.0654,0.0012</t>
+  </si>
+  <si>
+    <t>0.6026,0.3250,0.1113,0.0037</t>
+  </si>
+  <si>
+    <t>0.2846,0.6396,0.0918,0.0013</t>
+  </si>
+  <si>
+    <t>0.8768,0.1303,0.0127,0.0005</t>
+  </si>
+  <si>
+    <t>0.8199,0.0887,0.0727,0.0020</t>
+  </si>
+  <si>
+    <t>0.8826,0.0692,0.0303,0.0010</t>
+  </si>
+  <si>
+    <t>0.8110,0.1374,0.0462,0.0023</t>
+  </si>
+  <si>
+    <t>0.9725,0.0128,0.0051,0.0004</t>
+  </si>
+  <si>
+    <t>0.7096,0.3843,0.0095,0.0017</t>
+  </si>
+  <si>
+    <t>0.4444,0.6623,0.0096,0.0020</t>
+  </si>
+  <si>
+    <t>0.7221,0.3656,0.0066,0.0017</t>
+  </si>
+  <si>
+    <t>0.8915,0.1257,0.0036,0.0012</t>
+  </si>
+  <si>
+    <t>0.8059,0.2326,0.0087,0.0017</t>
+  </si>
+  <si>
+    <t>0.9600,0.0258,0.0079,0.0004</t>
+  </si>
+  <si>
+    <t>0.9297,0.0502,0.0145,0.0009</t>
+  </si>
+  <si>
+    <t>0.9645,0.0182,0.0070,0.0006</t>
+  </si>
+  <si>
+    <t>0.9269,0.0193,0.0560,0.0030</t>
+  </si>
+  <si>
+    <t>0.9101,0.0354,0.0352,0.0038</t>
+  </si>
+  <si>
+    <t>0.3617,0.0620,0.6489,0.0074</t>
+  </si>
+  <si>
+    <t>0.9534,0.0044,0.0725,0.0010</t>
+  </si>
+  <si>
+    <t>0.9630,0.0038,0.0492,0.0008</t>
+  </si>
+  <si>
+    <t>0.9594,0.0023,0.0763,0.0007</t>
+  </si>
+  <si>
+    <t>0.9679,0.0016,0.0645,0.0002</t>
+  </si>
+  <si>
+    <t>0.9747,0.0160,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.9215,0.0876,0.0029,0.0008</t>
+  </si>
+  <si>
+    <t>0.8180,0.1405,0.0079,0.0052</t>
+  </si>
+  <si>
+    <t>0.7849,0.2570,0.0078,0.0021</t>
+  </si>
+  <si>
+    <t>0.9055,0.0991,0.0031,0.0012</t>
+  </si>
+  <si>
+    <t>0.9479,0.0523,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.5879,0.4934,0.0058,0.0013</t>
+  </si>
+  <si>
+    <t>0.8211,0.1901,0.0072,0.0023</t>
+  </si>
+  <si>
+    <t>0.5554,0.2459,0.1126,0.0011</t>
+  </si>
+  <si>
+    <t>0.6818,0.3088,0.0562,0.0055</t>
+  </si>
+  <si>
+    <t>0.8927,0.1002,0.0065,0.0017</t>
+  </si>
+  <si>
+    <t>0.5646,0.0039,0.6996,0.0003</t>
+  </si>
+  <si>
+    <t>0.2411,0.1073,0.7753,0.0076</t>
+  </si>
+  <si>
+    <t>0.9472,0.0161,0.0299,0.0008</t>
+  </si>
+  <si>
+    <t>0.0588,0.0401,0.9563,0.0014</t>
+  </si>
+  <si>
+    <t>0.7537,0.0112,0.3834,0.0019</t>
+  </si>
+  <si>
+    <t>0.2022,0.1405,0.6573,0.0015</t>
+  </si>
+  <si>
+    <t>0.5681,0.0320,0.5547,0.0061</t>
+  </si>
+  <si>
+    <t>0.8751,0.0367,0.1398,0.0041</t>
+  </si>
+  <si>
+    <t>0.9679,0.0079,0.0152,0.0005</t>
+  </si>
+  <si>
+    <t>0.9607,0.0124,0.0196,0.0004</t>
+  </si>
+  <si>
+    <t>0.9441,0.0303,0.0183,0.0005</t>
+  </si>
+  <si>
+    <t>0.7121,0.2976,0.0053,0.0013</t>
+  </si>
+  <si>
+    <t>0.8577,0.1347,0.0028,0.0013</t>
+  </si>
+  <si>
+    <t>0.9127,0.1146,0.0016,0.0007</t>
+  </si>
+  <si>
+    <t>0.8475,0.1344,0.0029,0.0021</t>
+  </si>
+  <si>
+    <t>0.8090,0.2137,0.0032,0.0016</t>
+  </si>
+  <si>
+    <t>0.7977,0.2452,0.0090,0.0022</t>
+  </si>
+  <si>
+    <t>0.8605,0.1724,0.0032,0.0010</t>
+  </si>
+  <si>
+    <t>0.5776,0.5870,0.0117,0.0009</t>
+  </si>
+  <si>
+    <t>0.7992,0.0738,0.1292,0.0016</t>
+  </si>
+  <si>
+    <t>0.1198,0.0660,0.8727,0.0006</t>
+  </si>
+  <si>
+    <t>0.4440,0.0147,0.6663,0.0008</t>
+  </si>
+  <si>
+    <t>0.7108,0.0540,0.3222,0.0043</t>
+  </si>
+  <si>
+    <t>0.7827,0.0081,0.3506,0.0010</t>
+  </si>
+  <si>
+    <t>0.8800,0.0267,0.1028,0.0042</t>
+  </si>
+  <si>
+    <t>0.9059,0.0189,0.1069,0.0020</t>
+  </si>
+  <si>
+    <t>0.9215,0.0063,0.1199,0.0021</t>
+  </si>
+  <si>
+    <t>0.9057,0.0411,0.0382,0.0058</t>
+  </si>
+  <si>
+    <t>0.9029,0.0344,0.0424,0.0089</t>
+  </si>
+  <si>
+    <t>0.9394,0.0199,0.0067,0.0087</t>
+  </si>
+  <si>
+    <t>0.8161,0.0477,0.0386,0.0595</t>
+  </si>
+  <si>
+    <t>0.8574,0.0136,0.0097,0.0938</t>
+  </si>
+  <si>
+    <t>0.4732,0.5555,0.0564,0.0038</t>
   </si>
 </sst>
 </file>
@@ -2051,7 +2051,7 @@
         <v>259</v>
       </c>
       <c r="C9" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D9" t="s">
         <v>271</v>
@@ -2093,7 +2093,7 @@
         <v>259</v>
       </c>
       <c r="C12" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D12" t="s">
         <v>274</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3213,7 +3213,7 @@
         <v>259</v>
       </c>
       <c r="C92" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D92" t="s">
         <v>354</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3703,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
         <v>389</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4347,7 +4347,7 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
         <v>435</v>
@@ -4459,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
         <v>443</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4529,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
         <v>448</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4725,7 +4725,7 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
         <v>462</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5313,7 +5313,7 @@
         <v>259</v>
       </c>
       <c r="C242" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D242" t="s">
         <v>504</v>
@@ -5341,7 +5341,7 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
         <v>506</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5509,7 +5509,7 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D256" t="s">
         <v>518</v>

--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7404,0.3161,0.0150,0.0016</t>
-  </si>
-  <si>
-    <t>0.8781,0.0196,0.0205,0.0282</t>
-  </si>
-  <si>
-    <t>0.8214,0.1483,0.0177,0.0038</t>
-  </si>
-  <si>
-    <t>0.8661,0.0635,0.0232,0.0119</t>
-  </si>
-  <si>
-    <t>0.9020,0.1166,0.0031,0.0014</t>
-  </si>
-  <si>
-    <t>0.7467,0.3599,0.0048,0.0010</t>
-  </si>
-  <si>
-    <t>0.8446,0.1900,0.0071,0.0014</t>
-  </si>
-  <si>
-    <t>0.4174,0.6234,0.0392,0.0051</t>
-  </si>
-  <si>
-    <t>0.8803,0.1273,0.0024,0.0012</t>
-  </si>
-  <si>
-    <t>0.7104,0.3525,0.0112,0.0018</t>
-  </si>
-  <si>
-    <t>0.4631,0.6007,0.0284,0.0045</t>
-  </si>
-  <si>
-    <t>0.9099,0.1136,0.0031,0.0008</t>
-  </si>
-  <si>
-    <t>0.8951,0.0652,0.0211,0.0003</t>
-  </si>
-  <si>
-    <t>0.9265,0.0179,0.0560,0.0029</t>
-  </si>
-  <si>
-    <t>0.7913,0.0843,0.1021,0.0017</t>
-  </si>
-  <si>
-    <t>0.9342,0.0050,0.0997,0.0015</t>
-  </si>
-  <si>
-    <t>0.8600,0.1124,0.0288,0.0016</t>
-  </si>
-  <si>
-    <t>0.6916,0.4495,0.0068,0.0002</t>
-  </si>
-  <si>
-    <t>0.3739,0.7111,0.0283,0.0016</t>
-  </si>
-  <si>
-    <t>0.8320,0.2306,0.0053,0.0005</t>
-  </si>
-  <si>
-    <t>0.0688,0.9587,0.0048,0.0002</t>
-  </si>
-  <si>
-    <t>0.2097,0.8861,0.0069,0.0004</t>
-  </si>
-  <si>
-    <t>0.8446,0.0492,0.1240,0.0017</t>
-  </si>
-  <si>
-    <t>0.9723,0.0031,0.0358,0.0004</t>
-  </si>
-  <si>
-    <t>0.9597,0.0058,0.0425,0.0011</t>
-  </si>
-  <si>
-    <t>0.9218,0.0141,0.0844,0.0006</t>
-  </si>
-  <si>
-    <t>0.9515,0.0163,0.0289,0.0010</t>
-  </si>
-  <si>
-    <t>0.8503,0.0082,0.2706,0.0020</t>
-  </si>
-  <si>
-    <t>0.7929,0.0183,0.3092,0.0019</t>
-  </si>
-  <si>
-    <t>0.7045,0.3937,0.0155,0.0011</t>
-  </si>
-  <si>
-    <t>0.8946,0.0564,0.0470,0.0011</t>
-  </si>
-  <si>
-    <t>0.0634,0.4234,0.8977,0.0052</t>
-  </si>
-  <si>
-    <t>0.0857,0.7967,0.0695,0.0002</t>
-  </si>
-  <si>
-    <t>0.8580,0.1434,0.0038,0.0017</t>
-  </si>
-  <si>
-    <t>0.9535,0.0359,0.0074,0.0011</t>
-  </si>
-  <si>
-    <t>0.7315,0.3037,0.0155,0.0026</t>
-  </si>
-  <si>
-    <t>0.8119,0.1832,0.0348,0.0011</t>
-  </si>
-  <si>
-    <t>0.7845,0.0779,0.1035,0.0018</t>
-  </si>
-  <si>
-    <t>0.9624,0.0007,0.0755,0.0009</t>
-  </si>
-  <si>
-    <t>0.9330,0.0069,0.1085,0.0004</t>
-  </si>
-  <si>
-    <t>0.8669,0.0035,0.2692,0.0009</t>
-  </si>
-  <si>
-    <t>0.8867,0.0144,0.1517,0.0006</t>
-  </si>
-  <si>
-    <t>0.3440,0.2764,0.1717,0.0007</t>
-  </si>
-  <si>
-    <t>0.8293,0.0166,0.2496,0.0021</t>
-  </si>
-  <si>
-    <t>0.5527,0.5372,0.0229,0.0008</t>
-  </si>
-  <si>
-    <t>0.8863,0.1231,0.0077,0.0002</t>
-  </si>
-  <si>
-    <t>0.8758,0.0844,0.0246,0.0005</t>
-  </si>
-  <si>
-    <t>0.8862,0.1098,0.0126,0.0002</t>
-  </si>
-  <si>
-    <t>0.1396,0.1648,0.8129,0.0077</t>
-  </si>
-  <si>
-    <t>0.2820,0.0541,0.7561,0.0016</t>
-  </si>
-  <si>
-    <t>0.6712,0.0226,0.3645,0.0007</t>
-  </si>
-  <si>
-    <t>0.2386,0.0650,0.7294,0.0031</t>
-  </si>
-  <si>
-    <t>0.6230,0.0040,0.5554,0.0004</t>
-  </si>
-  <si>
-    <t>0.7272,0.0188,0.3602,0.0014</t>
-  </si>
-  <si>
-    <t>0.8259,0.1701,0.0079,0.0026</t>
-  </si>
-  <si>
-    <t>0.9680,0.0268,0.0017,0.0007</t>
-  </si>
-  <si>
-    <t>0.8457,0.1982,0.0028,0.0016</t>
-  </si>
-  <si>
-    <t>0.2543,0.5543,0.4742,0.0195</t>
-  </si>
-  <si>
-    <t>0.9806,0.0086,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.7362,0.2989,0.0141,0.0023</t>
-  </si>
-  <si>
-    <t>0.8856,0.1038,0.0042,0.0021</t>
-  </si>
-  <si>
-    <t>0.2246,0.3884,0.6133,0.0030</t>
-  </si>
-  <si>
-    <t>0.9037,0.0022,0.2448,0.0009</t>
-  </si>
-  <si>
-    <t>0.6138,0.0830,0.4734,0.0048</t>
-  </si>
-  <si>
-    <t>0.3259,0.0467,0.6752,0.0004</t>
-  </si>
-  <si>
-    <t>0.3839,0.0449,0.7185,0.0014</t>
-  </si>
-  <si>
-    <t>0.8739,0.1618,0.0063,0.0001</t>
-  </si>
-  <si>
-    <t>0.1713,0.8669,0.0158,0.0007</t>
-  </si>
-  <si>
-    <t>0.7258,0.1628,0.1015,0.0024</t>
-  </si>
-  <si>
-    <t>0.8368,0.2051,0.0090,0.0004</t>
-  </si>
-  <si>
-    <t>0.0450,0.3012,0.9127,0.0047</t>
-  </si>
-  <si>
-    <t>0.7476,0.0062,0.4585,0.0007</t>
-  </si>
-  <si>
-    <t>0.8153,0.0417,0.1798,0.0012</t>
-  </si>
-  <si>
-    <t>0.8473,0.0355,0.0969,0.0007</t>
-  </si>
-  <si>
-    <t>0.2355,0.4392,0.1524,0.0006</t>
-  </si>
-  <si>
-    <t>0.6294,0.1942,0.2812,0.0382</t>
-  </si>
-  <si>
-    <t>0.9098,0.0230,0.0039,0.0134</t>
-  </si>
-  <si>
-    <t>0.9181,0.0148,0.0137,0.0209</t>
-  </si>
-  <si>
-    <t>0.8610,0.0402,0.0113,0.0290</t>
-  </si>
-  <si>
-    <t>0.9523,0.0087,0.0074,0.0130</t>
-  </si>
-  <si>
-    <t>0.8091,0.1072,0.0193,0.0155</t>
-  </si>
-  <si>
-    <t>0.5427,0.0598,0.3911,0.0014</t>
-  </si>
-  <si>
-    <t>0.6659,0.0254,0.4209,0.0025</t>
-  </si>
-  <si>
-    <t>0.3575,0.0562,0.6556,0.0011</t>
-  </si>
-  <si>
-    <t>0.5722,0.1895,0.0781,0.0002</t>
-  </si>
-  <si>
-    <t>0.0516,0.7152,0.5258,0.0005</t>
-  </si>
-  <si>
-    <t>0.9585,0.0035,0.0587,0.0002</t>
-  </si>
-  <si>
-    <t>0.9027,0.1027,0.0031,0.0012</t>
-  </si>
-  <si>
-    <t>0.8562,0.1478,0.0067,0.0016</t>
-  </si>
-  <si>
-    <t>0.8004,0.2066,0.0053,0.0026</t>
-  </si>
-  <si>
-    <t>0.5603,0.5491,0.0166,0.0018</t>
-  </si>
-  <si>
-    <t>0.8833,0.1016,0.0024,0.0020</t>
-  </si>
-  <si>
-    <t>0.7009,0.3334,0.0082,0.0035</t>
-  </si>
-  <si>
-    <t>0.8623,0.1575,0.0049,0.0014</t>
-  </si>
-  <si>
-    <t>0.6414,0.4065,0.0106,0.0034</t>
-  </si>
-  <si>
-    <t>0.9546,0.0368,0.0031,0.0013</t>
-  </si>
-  <si>
-    <t>0.8177,0.2060,0.0069,0.0031</t>
-  </si>
-  <si>
-    <t>0.6964,0.3247,0.0178,0.0041</t>
-  </si>
-  <si>
-    <t>0.8188,0.2183,0.0042,0.0012</t>
-  </si>
-  <si>
-    <t>0.7428,0.3145,0.0075,0.0021</t>
-  </si>
-  <si>
-    <t>0.6802,0.3813,0.0109,0.0017</t>
-  </si>
-  <si>
-    <t>0.8979,0.1405,0.0026,0.0008</t>
-  </si>
-  <si>
-    <t>0.6970,0.3215,0.0159,0.0035</t>
-  </si>
-  <si>
-    <t>0.0847,0.2852,0.8782,0.0138</t>
-  </si>
-  <si>
-    <t>0.9418,0.0094,0.0472,0.0004</t>
-  </si>
-  <si>
-    <t>0.9569,0.0124,0.0204,0.0006</t>
-  </si>
-  <si>
-    <t>0.9096,0.0185,0.0945,0.0017</t>
-  </si>
-  <si>
-    <t>0.1887,0.8588,0.0204,0.0009</t>
-  </si>
-  <si>
-    <t>0.2825,0.8010,0.0118,0.0015</t>
-  </si>
-  <si>
-    <t>0.2730,0.8411,0.0064,0.0008</t>
-  </si>
-  <si>
-    <t>0.5462,0.6295,0.0079,0.0006</t>
-  </si>
-  <si>
-    <t>0.1316,0.8976,0.0165,0.0013</t>
-  </si>
-  <si>
-    <t>0.1114,0.9123,0.0160,0.0004</t>
-  </si>
-  <si>
-    <t>0.9646,0.0315,0.0022,0.0004</t>
-  </si>
-  <si>
-    <t>0.8548,0.1265,0.0272,0.0024</t>
-  </si>
-  <si>
-    <t>0.9103,0.0116,0.1132,0.0026</t>
-  </si>
-  <si>
-    <t>0.9469,0.0132,0.0387,0.0024</t>
-  </si>
-  <si>
-    <t>0.9278,0.0390,0.0220,0.0011</t>
-  </si>
-  <si>
-    <t>0.7271,0.1876,0.1232,0.0139</t>
-  </si>
-  <si>
-    <t>0.8775,0.1662,0.0061,0.0001</t>
-  </si>
-  <si>
-    <t>0.3285,0.6912,0.0113,0.0001</t>
-  </si>
-  <si>
-    <t>0.6857,0.3000,0.0652,0.0019</t>
-  </si>
-  <si>
-    <t>0.3673,0.6242,0.0169,0.0003</t>
-  </si>
-  <si>
-    <t>0.8799,0.1586,0.0046,0.0004</t>
-  </si>
-  <si>
-    <t>0.7263,0.3194,0.0188,0.0018</t>
-  </si>
-  <si>
-    <t>0.4605,0.5842,0.0137,0.0026</t>
-  </si>
-  <si>
-    <t>0.8576,0.1985,0.0060,0.0006</t>
-  </si>
-  <si>
-    <t>0.9402,0.0541,0.0024,0.0018</t>
-  </si>
-  <si>
-    <t>0.7920,0.2729,0.0108,0.0020</t>
-  </si>
-  <si>
-    <t>0.8177,0.2066,0.0164,0.0022</t>
-  </si>
-  <si>
-    <t>0.8227,0.2147,0.0112,0.0020</t>
-  </si>
-  <si>
-    <t>0.9288,0.0790,0.0042,0.0011</t>
-  </si>
-  <si>
-    <t>0.6584,0.4403,0.0040,0.0011</t>
-  </si>
-  <si>
-    <t>0.8035,0.2422,0.0056,0.0018</t>
-  </si>
-  <si>
-    <t>0.6969,0.0111,0.5323,0.0026</t>
-  </si>
-  <si>
-    <t>0.7047,0.0066,0.5138,0.0010</t>
-  </si>
-  <si>
-    <t>0.8159,0.0048,0.3299,0.0012</t>
-  </si>
-  <si>
-    <t>0.6690,0.0059,0.5566,0.0021</t>
-  </si>
-  <si>
-    <t>0.9036,0.0678,0.0151,0.0015</t>
-  </si>
-  <si>
-    <t>0.9607,0.0178,0.0120,0.0008</t>
-  </si>
-  <si>
-    <t>0.8251,0.0539,0.1619,0.0043</t>
-  </si>
-  <si>
-    <t>0.9489,0.0278,0.0116,0.0005</t>
-  </si>
-  <si>
-    <t>0.9214,0.0320,0.0166,0.0066</t>
-  </si>
-  <si>
-    <t>0.8194,0.0652,0.0825,0.0419</t>
-  </si>
-  <si>
-    <t>0.9436,0.0099,0.0075,0.0155</t>
-  </si>
-  <si>
-    <t>0.9316,0.0202,0.0107,0.0108</t>
-  </si>
-  <si>
-    <t>0.3524,0.5590,0.0305,0.0002</t>
-  </si>
-  <si>
-    <t>0.5998,0.4462,0.0187,0.0084</t>
-  </si>
-  <si>
-    <t>0.7643,0.2291,0.0237,0.0037</t>
-  </si>
-  <si>
-    <t>0.8050,0.1526,0.0142,0.0061</t>
-  </si>
-  <si>
-    <t>0.5482,0.5746,0.0150,0.0016</t>
-  </si>
-  <si>
-    <t>0.8992,0.1053,0.0067,0.0015</t>
-  </si>
-  <si>
-    <t>0.9099,0.0560,0.0159,0.0039</t>
-  </si>
-  <si>
-    <t>0.8199,0.2068,0.0054,0.0017</t>
-  </si>
-  <si>
-    <t>0.3268,0.3532,0.6216,0.0176</t>
-  </si>
-  <si>
-    <t>0.9004,0.0497,0.0289,0.0050</t>
-  </si>
-  <si>
-    <t>0.7527,0.2098,0.0239,0.0089</t>
-  </si>
-  <si>
-    <t>0.5623,0.5342,0.0227,0.0011</t>
-  </si>
-  <si>
-    <t>0.7499,0.1948,0.0092,0.0040</t>
-  </si>
-  <si>
-    <t>0.8197,0.2315,0.0105,0.0017</t>
-  </si>
-  <si>
-    <t>0.8738,0.0791,0.0344,0.0036</t>
-  </si>
-  <si>
-    <t>0.8532,0.1470,0.0160,0.0013</t>
-  </si>
-  <si>
-    <t>0.8558,0.1829,0.0095,0.0017</t>
-  </si>
-  <si>
-    <t>0.7018,0.3629,0.0139,0.0031</t>
-  </si>
-  <si>
-    <t>0.9211,0.0319,0.0006,0.0028</t>
-  </si>
-  <si>
-    <t>0.7944,0.2108,0.0046,0.0034</t>
-  </si>
-  <si>
-    <t>0.8752,0.1285,0.0035,0.0017</t>
-  </si>
-  <si>
-    <t>0.9359,0.0445,0.0019,0.0020</t>
-  </si>
-  <si>
-    <t>0.8226,0.1543,0.0146,0.0059</t>
-  </si>
-  <si>
-    <t>0.7659,0.3116,0.0096,0.0011</t>
-  </si>
-  <si>
-    <t>0.8985,0.1034,0.0053,0.0030</t>
-  </si>
-  <si>
-    <t>0.8188,0.1976,0.0225,0.0013</t>
-  </si>
-  <si>
-    <t>0.7577,0.2493,0.0144,0.0039</t>
-  </si>
-  <si>
-    <t>0.6114,0.4791,0.0216,0.0019</t>
-  </si>
-  <si>
-    <t>0.3582,0.5704,0.2128,0.0043</t>
-  </si>
-  <si>
-    <t>0.8186,0.1846,0.0024,0.0018</t>
-  </si>
-  <si>
-    <t>0.9275,0.0557,0.0069,0.0021</t>
-  </si>
-  <si>
-    <t>0.7720,0.2994,0.0098,0.0022</t>
-  </si>
-  <si>
-    <t>0.5902,0.4631,0.0371,0.0029</t>
-  </si>
-  <si>
-    <t>0.0561,0.0542,0.9247,0.0019</t>
-  </si>
-  <si>
-    <t>0.9435,0.0506,0.0038,0.0007</t>
-  </si>
-  <si>
-    <t>0.1724,0.0043,0.8979,0.0006</t>
-  </si>
-  <si>
-    <t>0.8212,0.0044,0.3668,0.0007</t>
-  </si>
-  <si>
-    <t>0.8932,0.0076,0.1975,0.0023</t>
-  </si>
-  <si>
-    <t>0.3687,0.1144,0.6960,0.0014</t>
-  </si>
-  <si>
-    <t>0.2186,0.2728,0.4875,0.0009</t>
-  </si>
-  <si>
-    <t>0.8535,0.0078,0.2638,0.0013</t>
-  </si>
-  <si>
-    <t>0.7995,0.0553,0.2202,0.0024</t>
-  </si>
-  <si>
-    <t>0.9357,0.0136,0.0654,0.0012</t>
-  </si>
-  <si>
-    <t>0.6026,0.3250,0.1113,0.0037</t>
-  </si>
-  <si>
-    <t>0.2846,0.6396,0.0918,0.0013</t>
-  </si>
-  <si>
-    <t>0.8768,0.1303,0.0127,0.0005</t>
-  </si>
-  <si>
-    <t>0.8199,0.0887,0.0727,0.0020</t>
-  </si>
-  <si>
-    <t>0.8826,0.0692,0.0303,0.0010</t>
-  </si>
-  <si>
-    <t>0.8110,0.1374,0.0462,0.0023</t>
-  </si>
-  <si>
-    <t>0.9725,0.0128,0.0051,0.0004</t>
-  </si>
-  <si>
-    <t>0.7096,0.3843,0.0095,0.0017</t>
-  </si>
-  <si>
-    <t>0.4444,0.6623,0.0096,0.0020</t>
-  </si>
-  <si>
-    <t>0.7221,0.3656,0.0066,0.0017</t>
-  </si>
-  <si>
-    <t>0.8915,0.1257,0.0036,0.0012</t>
-  </si>
-  <si>
-    <t>0.8059,0.2326,0.0087,0.0017</t>
-  </si>
-  <si>
-    <t>0.9600,0.0258,0.0079,0.0004</t>
-  </si>
-  <si>
-    <t>0.9297,0.0502,0.0145,0.0009</t>
-  </si>
-  <si>
-    <t>0.9645,0.0182,0.0070,0.0006</t>
-  </si>
-  <si>
-    <t>0.9269,0.0193,0.0560,0.0030</t>
-  </si>
-  <si>
-    <t>0.9101,0.0354,0.0352,0.0038</t>
-  </si>
-  <si>
-    <t>0.3617,0.0620,0.6489,0.0074</t>
-  </si>
-  <si>
-    <t>0.9534,0.0044,0.0725,0.0010</t>
-  </si>
-  <si>
-    <t>0.9630,0.0038,0.0492,0.0008</t>
-  </si>
-  <si>
-    <t>0.9594,0.0023,0.0763,0.0007</t>
-  </si>
-  <si>
-    <t>0.9679,0.0016,0.0645,0.0002</t>
-  </si>
-  <si>
-    <t>0.9747,0.0160,0.0007,0.0009</t>
-  </si>
-  <si>
-    <t>0.9215,0.0876,0.0029,0.0008</t>
-  </si>
-  <si>
-    <t>0.8180,0.1405,0.0079,0.0052</t>
-  </si>
-  <si>
-    <t>0.7849,0.2570,0.0078,0.0021</t>
-  </si>
-  <si>
-    <t>0.9055,0.0991,0.0031,0.0012</t>
-  </si>
-  <si>
-    <t>0.9479,0.0523,0.0016,0.0005</t>
-  </si>
-  <si>
-    <t>0.5879,0.4934,0.0058,0.0013</t>
-  </si>
-  <si>
-    <t>0.8211,0.1901,0.0072,0.0023</t>
-  </si>
-  <si>
-    <t>0.5554,0.2459,0.1126,0.0011</t>
-  </si>
-  <si>
-    <t>0.6818,0.3088,0.0562,0.0055</t>
-  </si>
-  <si>
-    <t>0.8927,0.1002,0.0065,0.0017</t>
-  </si>
-  <si>
-    <t>0.5646,0.0039,0.6996,0.0003</t>
-  </si>
-  <si>
-    <t>0.2411,0.1073,0.7753,0.0076</t>
-  </si>
-  <si>
-    <t>0.9472,0.0161,0.0299,0.0008</t>
-  </si>
-  <si>
-    <t>0.0588,0.0401,0.9563,0.0014</t>
-  </si>
-  <si>
-    <t>0.7537,0.0112,0.3834,0.0019</t>
-  </si>
-  <si>
-    <t>0.2022,0.1405,0.6573,0.0015</t>
-  </si>
-  <si>
-    <t>0.5681,0.0320,0.5547,0.0061</t>
-  </si>
-  <si>
-    <t>0.8751,0.0367,0.1398,0.0041</t>
-  </si>
-  <si>
-    <t>0.9679,0.0079,0.0152,0.0005</t>
-  </si>
-  <si>
-    <t>0.9607,0.0124,0.0196,0.0004</t>
-  </si>
-  <si>
-    <t>0.9441,0.0303,0.0183,0.0005</t>
-  </si>
-  <si>
-    <t>0.7121,0.2976,0.0053,0.0013</t>
-  </si>
-  <si>
-    <t>0.8577,0.1347,0.0028,0.0013</t>
-  </si>
-  <si>
-    <t>0.9127,0.1146,0.0016,0.0007</t>
-  </si>
-  <si>
-    <t>0.8475,0.1344,0.0029,0.0021</t>
-  </si>
-  <si>
-    <t>0.8090,0.2137,0.0032,0.0016</t>
-  </si>
-  <si>
-    <t>0.7977,0.2452,0.0090,0.0022</t>
-  </si>
-  <si>
-    <t>0.8605,0.1724,0.0032,0.0010</t>
-  </si>
-  <si>
-    <t>0.5776,0.5870,0.0117,0.0009</t>
-  </si>
-  <si>
-    <t>0.7992,0.0738,0.1292,0.0016</t>
-  </si>
-  <si>
-    <t>0.1198,0.0660,0.8727,0.0006</t>
-  </si>
-  <si>
-    <t>0.4440,0.0147,0.6663,0.0008</t>
-  </si>
-  <si>
-    <t>0.7108,0.0540,0.3222,0.0043</t>
-  </si>
-  <si>
-    <t>0.7827,0.0081,0.3506,0.0010</t>
-  </si>
-  <si>
-    <t>0.8800,0.0267,0.1028,0.0042</t>
-  </si>
-  <si>
-    <t>0.9059,0.0189,0.1069,0.0020</t>
-  </si>
-  <si>
-    <t>0.9215,0.0063,0.1199,0.0021</t>
-  </si>
-  <si>
-    <t>0.9057,0.0411,0.0382,0.0058</t>
-  </si>
-  <si>
-    <t>0.9029,0.0344,0.0424,0.0089</t>
-  </si>
-  <si>
-    <t>0.9394,0.0199,0.0067,0.0087</t>
-  </si>
-  <si>
-    <t>0.8161,0.0477,0.0386,0.0595</t>
-  </si>
-  <si>
-    <t>0.8574,0.0136,0.0097,0.0938</t>
-  </si>
-  <si>
-    <t>0.4732,0.5555,0.0564,0.0038</t>
+    <t>0.9518,0.0083,0.0101,0.0182</t>
+  </si>
+  <si>
+    <t>0.0159,0.0052,0.0002,0.9932</t>
+  </si>
+  <si>
+    <t>0.8876,0.0022,0.0005,0.1218</t>
+  </si>
+  <si>
+    <t>0.2344,0.0103,0.0004,0.8650</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9941,0.0021,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9985,0.0002,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9980,0.0015,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9960,0.0020,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9968,0.0006,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.6688,0.0229,0.3991,0.0065</t>
+  </si>
+  <si>
+    <t>0.3375,0.0329,0.7121,0.0117</t>
+  </si>
+  <si>
+    <t>0.5261,0.0017,0.7625,0.0002</t>
+  </si>
+  <si>
+    <t>0.2289,0.0133,0.7980,0.0160</t>
+  </si>
+  <si>
+    <t>0.9268,0.0081,0.0955,0.0008</t>
+  </si>
+  <si>
+    <t>0.0278,0.9788,0.0013,0.0009</t>
+  </si>
+  <si>
+    <t>0.0014,0.9962,0.0010,0.0024</t>
+  </si>
+  <si>
+    <t>0.1754,0.8715,0.0094,0.0029</t>
+  </si>
+  <si>
+    <t>0.0554,0.9667,0.0012,0.0011</t>
+  </si>
+  <si>
+    <t>0.0053,0.9924,0.0032,0.0011</t>
+  </si>
+  <si>
+    <t>0.6820,0.0098,0.4273,0.0067</t>
+  </si>
+  <si>
+    <t>0.6174,0.0097,0.4489,0.0087</t>
+  </si>
+  <si>
+    <t>0.0064,0.0030,0.9863,0.0040</t>
+  </si>
+  <si>
+    <t>0.0681,0.0053,0.9355,0.0040</t>
+  </si>
+  <si>
+    <t>0.1650,0.0013,0.9124,0.0010</t>
+  </si>
+  <si>
+    <t>0.0595,0.0024,0.9634,0.0012</t>
+  </si>
+  <si>
+    <t>0.0038,0.0022,0.9930,0.0027</t>
+  </si>
+  <si>
+    <t>0.1082,0.9124,0.0136,0.0179</t>
+  </si>
+  <si>
+    <t>0.8683,0.1200,0.0283,0.0146</t>
+  </si>
+  <si>
+    <t>0.0057,0.0144,0.9924,0.0021</t>
+  </si>
+  <si>
+    <t>0.0325,0.4571,0.5281,0.0003</t>
+  </si>
+  <si>
+    <t>0.9061,0.0584,0.0270,0.0203</t>
+  </si>
+  <si>
+    <t>0.9076,0.0688,0.0295,0.0049</t>
+  </si>
+  <si>
+    <t>0.9604,0.0610,0.0027,0.0009</t>
+  </si>
+  <si>
+    <t>0.0152,0.9624,0.2566,0.0010</t>
+  </si>
+  <si>
+    <t>0.0168,0.3377,0.9044,0.0046</t>
+  </si>
+  <si>
+    <t>0.0175,0.0049,0.9649,0.0187</t>
+  </si>
+  <si>
+    <t>0.3384,0.0083,0.7576,0.0018</t>
+  </si>
+  <si>
+    <t>0.2060,0.0009,0.4999,0.0867</t>
+  </si>
+  <si>
+    <t>0.0270,0.2144,0.9573,0.0035</t>
+  </si>
+  <si>
+    <t>0.0177,0.8452,0.1561,0.0018</t>
+  </si>
+  <si>
+    <t>0.0652,0.0068,0.9429,0.0043</t>
+  </si>
+  <si>
+    <t>0.3050,0.2664,0.0500,0.5864</t>
+  </si>
+  <si>
+    <t>0.0025,0.9895,0.0042,0.0037</t>
+  </si>
+  <si>
+    <t>0.0064,0.9788,0.0287,0.0019</t>
+  </si>
+  <si>
+    <t>0.0026,0.9934,0.0079,0.0006</t>
+  </si>
+  <si>
+    <t>0.0010,0.0892,0.9869,0.0156</t>
+  </si>
+  <si>
+    <t>0.0021,0.2168,0.9865,0.0016</t>
+  </si>
+  <si>
+    <t>0.0339,0.0082,0.9471,0.0136</t>
+  </si>
+  <si>
+    <t>0.0218,0.0060,0.9813,0.0020</t>
+  </si>
+  <si>
+    <t>0.0249,0.0545,0.9315,0.0198</t>
+  </si>
+  <si>
+    <t>0.0049,0.0085,0.9886,0.0014</t>
+  </si>
+  <si>
+    <t>0.9741,0.0335,0.0016,0.0006</t>
+  </si>
+  <si>
+    <t>0.9952,0.0015,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9964,0.0006,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.0266,0.0765,0.9822,0.0015</t>
+  </si>
+  <si>
+    <t>0.9974,0.0007,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9973,0.0016,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9922,0.0071,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.9695,0.9900,0.0003</t>
+  </si>
+  <si>
+    <t>0.0170,0.0505,0.9834,0.0031</t>
+  </si>
+  <si>
+    <t>0.0067,0.0371,0.9755,0.0153</t>
+  </si>
+  <si>
+    <t>0.0007,0.9739,0.9753,0.0005</t>
+  </si>
+  <si>
+    <t>0.0021,0.0526,0.9935,0.0012</t>
+  </si>
+  <si>
+    <t>0.1241,0.8498,0.0725,0.0043</t>
+  </si>
+  <si>
+    <t>0.0121,0.9883,0.0075,0.0002</t>
+  </si>
+  <si>
+    <t>0.6633,0.0455,0.4829,0.0067</t>
+  </si>
+  <si>
+    <t>0.0670,0.1546,0.8974,0.0116</t>
+  </si>
+  <si>
+    <t>0.0100,0.0250,0.9853,0.0118</t>
+  </si>
+  <si>
+    <t>0.0031,0.8159,0.9585,0.0011</t>
+  </si>
+  <si>
+    <t>0.0120,0.7607,0.7097,0.0025</t>
+  </si>
+  <si>
+    <t>0.0011,0.9944,0.2117,0.0008</t>
+  </si>
+  <si>
+    <t>0.0044,0.9604,0.3788,0.0024</t>
+  </si>
+  <si>
+    <t>0.0251,0.0005,0.0014,0.9912</t>
+  </si>
+  <si>
+    <t>0.0013,0.0065,0.0003,0.9988</t>
+  </si>
+  <si>
+    <t>0.0024,0.0045,0.0001,0.9986</t>
+  </si>
+  <si>
+    <t>0.0108,0.0013,0.0015,0.9948</t>
+  </si>
+  <si>
+    <t>0.0057,0.0003,0.0007,0.9975</t>
+  </si>
+  <si>
+    <t>0.0013,0.0019,0.0004,0.9989</t>
+  </si>
+  <si>
+    <t>0.0045,0.9558,0.7746,0.0024</t>
+  </si>
+  <si>
+    <t>0.0019,0.8975,0.9779,0.0010</t>
+  </si>
+  <si>
+    <t>0.0152,0.4612,0.8968,0.0061</t>
+  </si>
+  <si>
+    <t>0.0041,0.3497,0.9813,0.0016</t>
+  </si>
+  <si>
+    <t>0.0027,0.9732,0.6751,0.0012</t>
+  </si>
+  <si>
+    <t>0.0132,0.6291,0.6725,0.0031</t>
+  </si>
+  <si>
+    <t>0.9975,0.0003,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9931,0.0063,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9929,0.0089,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9965,0.0011,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9968,0.0010,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9945,0.0031,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9912,0.0043,0.0043,0.0008</t>
+  </si>
+  <si>
+    <t>0.9909,0.0088,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9975,0.0015,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0002,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9977,0.0004,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9917,0.0086,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9973,0.0009,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9974,0.0007,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.0233,0.0386,0.9778,0.0023</t>
+  </si>
+  <si>
+    <t>0.0389,0.0017,0.9729,0.0010</t>
+  </si>
+  <si>
+    <t>0.7426,0.0098,0.2028,0.0436</t>
+  </si>
+  <si>
+    <t>0.0077,0.0017,0.9914,0.0009</t>
+  </si>
+  <si>
+    <t>0.0177,0.9813,0.0017,0.0010</t>
+  </si>
+  <si>
+    <t>0.0070,0.9901,0.0024,0.0003</t>
+  </si>
+  <si>
+    <t>0.0469,0.9595,0.0033,0.0037</t>
+  </si>
+  <si>
+    <t>0.1562,0.8823,0.0174,0.0029</t>
+  </si>
+  <si>
+    <t>0.0186,0.9769,0.0039,0.0020</t>
+  </si>
+  <si>
+    <t>0.0061,0.9904,0.0043,0.0006</t>
+  </si>
+  <si>
+    <t>0.5813,0.6727,0.0028,0.0002</t>
+  </si>
+  <si>
+    <t>0.8349,0.0542,0.1149,0.0168</t>
+  </si>
+  <si>
+    <t>0.0285,0.0056,0.9709,0.0046</t>
+  </si>
+  <si>
+    <t>0.6379,0.0375,0.3201,0.0577</t>
+  </si>
+  <si>
+    <t>0.4524,0.0183,0.6514,0.0139</t>
+  </si>
+  <si>
+    <t>0.1099,0.1989,0.2683,0.6167</t>
+  </si>
+  <si>
+    <t>0.0045,0.9923,0.0042,0.0003</t>
+  </si>
+  <si>
+    <t>0.0054,0.9878,0.0089,0.0010</t>
+  </si>
+  <si>
+    <t>0.0014,0.9949,0.0044,0.0011</t>
+  </si>
+  <si>
+    <t>0.0027,0.9482,0.6511,0.0019</t>
+  </si>
+  <si>
+    <t>0.0096,0.9875,0.0058,0.0003</t>
+  </si>
+  <si>
+    <t>0.7405,0.3779,0.0130,0.0011</t>
+  </si>
+  <si>
+    <t>0.9282,0.0879,0.0033,0.0027</t>
+  </si>
+  <si>
+    <t>0.9967,0.0007,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9980,0.0001,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9958,0.0009,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9833,0.0076,0.0050,0.0023</t>
+  </si>
+  <si>
+    <t>0.9979,0.0002,0.0001,0.0013</t>
+  </si>
+  <si>
+    <t>0.9956,0.0014,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.9980,0.0006,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9952,0.0017,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.0024,0.7560,0.9794,0.0032</t>
+  </si>
+  <si>
+    <t>0.0010,0.8033,0.9894,0.0004</t>
+  </si>
+  <si>
+    <t>0.0366,0.0967,0.9095,0.0186</t>
+  </si>
+  <si>
+    <t>0.0604,0.0318,0.9216,0.0036</t>
+  </si>
+  <si>
+    <t>0.9927,0.0009,0.0044,0.0004</t>
+  </si>
+  <si>
+    <t>0.7499,0.0160,0.2387,0.0180</t>
+  </si>
+  <si>
+    <t>0.1218,0.0098,0.8970,0.0072</t>
+  </si>
+  <si>
+    <t>0.8817,0.0266,0.1175,0.0090</t>
+  </si>
+  <si>
+    <t>0.0781,0.0004,0.0002,0.9869</t>
+  </si>
+  <si>
+    <t>0.0003,0.0029,0.0007,0.9994</t>
+  </si>
+  <si>
+    <t>0.0014,0.0031,0.0005,0.9987</t>
+  </si>
+  <si>
+    <t>0.0041,0.0001,0.0003,0.9986</t>
+  </si>
+  <si>
+    <t>0.0033,0.9701,0.7312,0.0020</t>
+  </si>
+  <si>
+    <t>0.9967,0.0007,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.5422,0.5910,0.0024,0.0024</t>
+  </si>
+  <si>
+    <t>0.9862,0.0078,0.0028,0.0017</t>
+  </si>
+  <si>
+    <t>0.7037,0.4396,0.0027,0.0036</t>
+  </si>
+  <si>
+    <t>0.9866,0.0019,0.0065,0.0020</t>
+  </si>
+  <si>
+    <t>0.1177,0.0054,0.0075,0.9250</t>
+  </si>
+  <si>
+    <t>0.9954,0.0011,0.0005,0.0010</t>
+  </si>
+  <si>
+    <t>0.0044,0.0127,0.8928,0.3874</t>
+  </si>
+  <si>
+    <t>0.9500,0.0002,0.0006,0.1007</t>
+  </si>
+  <si>
+    <t>0.9819,0.0005,0.0003,0.0185</t>
+  </si>
+  <si>
+    <t>0.1803,0.8719,0.0162,0.0034</t>
+  </si>
+  <si>
+    <t>0.9680,0.0181,0.0042,0.0034</t>
+  </si>
+  <si>
+    <t>0.9500,0.0314,0.0172,0.0042</t>
+  </si>
+  <si>
+    <t>0.3003,0.6388,0.0931,0.0114</t>
+  </si>
+  <si>
+    <t>0.9773,0.0166,0.0033,0.0008</t>
+  </si>
+  <si>
+    <t>0.9859,0.0070,0.0029,0.0007</t>
+  </si>
+  <si>
+    <t>0.9951,0.0026,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9976,0.0005,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9974,0.0007,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9966,0.0001,0.0003,0.0028</t>
+  </si>
+  <si>
+    <t>0.9985,0.0002,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9978,0.0004,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9948,0.0004,0.0025,0.0012</t>
+  </si>
+  <si>
+    <t>0.9975,0.0001,0.0000,0.0016</t>
+  </si>
+  <si>
+    <t>0.9068,0.0897,0.0050,0.0065</t>
+  </si>
+  <si>
+    <t>0.7057,0.4224,0.0081,0.0013</t>
+  </si>
+  <si>
+    <t>0.8382,0.2464,0.0074,0.0010</t>
+  </si>
+  <si>
+    <t>0.0877,0.1789,0.9160,0.0026</t>
+  </si>
+  <si>
+    <t>0.9944,0.0015,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9819,0.0059,0.0041,0.0028</t>
+  </si>
+  <si>
+    <t>0.9964,0.0013,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9776,0.0247,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.0008,0.0075,0.9987,0.0007</t>
+  </si>
+  <si>
+    <t>0.9563,0.0129,0.0288,0.0031</t>
+  </si>
+  <si>
+    <t>0.0014,0.0039,0.9926,0.0066</t>
+  </si>
+  <si>
+    <t>0.0028,0.0258,0.9953,0.0012</t>
+  </si>
+  <si>
+    <t>0.0290,0.0094,0.9707,0.0029</t>
+  </si>
+  <si>
+    <t>0.0240,0.0576,0.9766,0.0019</t>
+  </si>
+  <si>
+    <t>0.0054,0.0168,0.9820,0.0039</t>
+  </si>
+  <si>
+    <t>0.0016,0.0007,0.9980,0.0003</t>
+  </si>
+  <si>
+    <t>0.0027,0.0263,0.9929,0.0021</t>
+  </si>
+  <si>
+    <t>0.6329,0.0084,0.5098,0.0045</t>
+  </si>
+  <si>
+    <t>0.1784,0.0113,0.8526,0.0105</t>
+  </si>
+  <si>
+    <t>0.1676,0.0058,0.8730,0.0057</t>
+  </si>
+  <si>
+    <t>0.0794,0.5691,0.2713,0.0042</t>
+  </si>
+  <si>
+    <t>0.3118,0.1624,0.4795,0.0105</t>
+  </si>
+  <si>
+    <t>0.8564,0.0258,0.1719,0.0019</t>
+  </si>
+  <si>
+    <t>0.4570,0.0673,0.5370,0.0396</t>
+  </si>
+  <si>
+    <t>0.2654,0.0932,0.6991,0.0125</t>
+  </si>
+  <si>
+    <t>0.6365,0.5935,0.0053,0.0009</t>
+  </si>
+  <si>
+    <t>0.0266,0.9853,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9024,0.2568,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9868,0.0136,0.0015,0.0008</t>
+  </si>
+  <si>
+    <t>0.9484,0.0917,0.0014,0.0010</t>
+  </si>
+  <si>
+    <t>0.9051,0.0088,0.0652,0.0200</t>
+  </si>
+  <si>
+    <t>0.9068,0.0224,0.0627,0.0074</t>
+  </si>
+  <si>
+    <t>0.8811,0.0103,0.0468,0.0407</t>
+  </si>
+  <si>
+    <t>0.3798,0.1536,0.5299,0.0355</t>
+  </si>
+  <si>
+    <t>0.6463,0.0206,0.1878,0.1130</t>
+  </si>
+  <si>
+    <t>0.0136,0.0082,0.9732,0.0089</t>
+  </si>
+  <si>
+    <t>0.0416,0.0394,0.9160,0.0184</t>
+  </si>
+  <si>
+    <t>0.1372,0.0743,0.8380,0.0126</t>
+  </si>
+  <si>
+    <t>0.0739,0.0108,0.9454,0.0017</t>
+  </si>
+  <si>
+    <t>0.0408,0.5281,0.5480,0.0146</t>
+  </si>
+  <si>
+    <t>0.9892,0.0042,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.9949,0.0021,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.9206,0.1123,0.0040,0.0030</t>
+  </si>
+  <si>
+    <t>0.9986,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9956,0.0031,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9963,0.0024,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9934,0.0023,0.0003,0.0016</t>
+  </si>
+  <si>
+    <t>0.9941,0.0020,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.0212,0.1154,0.9769,0.0041</t>
+  </si>
+  <si>
+    <t>0.2051,0.6399,0.1683,0.0037</t>
+  </si>
+  <si>
+    <t>0.8931,0.0109,0.0906,0.0109</t>
+  </si>
+  <si>
+    <t>0.0042,0.0017,0.9969,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0053,0.9942,0.0123</t>
+  </si>
+  <si>
+    <t>0.0047,0.0397,0.9850,0.0045</t>
+  </si>
+  <si>
+    <t>0.0086,0.0416,0.9905,0.0007</t>
+  </si>
+  <si>
+    <t>0.0135,0.0095,0.9678,0.0073</t>
+  </si>
+  <si>
+    <t>0.0018,0.0104,0.9928,0.0063</t>
+  </si>
+  <si>
+    <t>0.0170,0.0357,0.9729,0.0036</t>
+  </si>
+  <si>
+    <t>0.0055,0.0599,0.9442,0.0503</t>
+  </si>
+  <si>
+    <t>0.6028,0.0196,0.3967,0.0301</t>
+  </si>
+  <si>
+    <t>0.5407,0.0038,0.6519,0.0013</t>
+  </si>
+  <si>
+    <t>0.8785,0.0035,0.2032,0.0030</t>
+  </si>
+  <si>
+    <t>0.9933,0.0068,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9978,0.0015,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9971,0.0007,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9960,0.0023,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9981,0.0001,0.0001,0.0013</t>
+  </si>
+  <si>
+    <t>0.9982,0.0004,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9954,0.0016,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9970,0.0012,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.0045,0.0575,0.9802,0.0016</t>
+  </si>
+  <si>
+    <t>0.0023,0.0947,0.9932,0.0011</t>
+  </si>
+  <si>
+    <t>0.0045,0.0039,0.9911,0.0017</t>
+  </si>
+  <si>
+    <t>0.0150,0.0028,0.9816,0.0009</t>
+  </si>
+  <si>
+    <t>0.1845,0.0021,0.8508,0.0034</t>
+  </si>
+  <si>
+    <t>0.0567,0.0315,0.8595,0.1227</t>
+  </si>
+  <si>
+    <t>0.4499,0.0068,0.7250,0.0030</t>
+  </si>
+  <si>
+    <t>0.0680,0.0061,0.9038,0.0309</t>
+  </si>
+  <si>
+    <t>0.4274,0.0014,0.0011,0.8261</t>
+  </si>
+  <si>
+    <t>0.1482,0.0032,0.0023,0.9512</t>
+  </si>
+  <si>
+    <t>0.2861,0.0022,0.0016,0.8677</t>
+  </si>
+  <si>
+    <t>0.0045,0.0001,0.0003,0.9983</t>
+  </si>
+  <si>
+    <t>0.0046,0.0002,0.0006,0.9976</t>
+  </si>
+  <si>
+    <t>0.9904,0.0017,0.0022,0.0015</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2051,7 +2051,7 @@
         <v>259</v>
       </c>
       <c r="C9" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D9" t="s">
         <v>271</v>
@@ -2093,7 +2093,7 @@
         <v>259</v>
       </c>
       <c r="C12" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D12" t="s">
         <v>274</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2919,7 +2919,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3213,7 +3213,7 @@
         <v>259</v>
       </c>
       <c r="C92" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D92" t="s">
         <v>354</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3591,7 +3591,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
         <v>381</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3703,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
         <v>389</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4081,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>416</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4585,7 +4585,7 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
         <v>452</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4669,7 +4669,7 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
         <v>458</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4809,7 +4809,7 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
         <v>468</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5187,7 +5187,7 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
         <v>495</v>
@@ -5313,7 +5313,7 @@
         <v>259</v>
       </c>
       <c r="C242" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D242" t="s">
         <v>504</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5439,7 +5439,7 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
         <v>513</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
@@ -5509,7 +5509,7 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
         <v>518</v>
